--- a/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T09:12:31+00:00</t>
+    <t>2026-03-16T15:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:56:46+00:00</t>
+    <t>2026-03-16T15:58:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:58:44+00:00</t>
+    <t>2026-03-16T16:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nr-init-ruim/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:04:23+00:00</t>
+    <t>2026-03-24T16:06:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
